--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/oct-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1978,7 +2058,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>820-39-CM25</t>
+          <t>692277-114-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,32 +2078,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2113,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8413.5</v>
+        <v>16313.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>692277-114-CM25</t>
+          <t>820-39-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,42 +2139,46 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>16313.97</v>
+        <v>8413.5</v>
       </c>
     </row>
     <row r="28">
@@ -2209,7 +2293,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2358,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2283,7 +2375,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2429-2700-CM25</t>
+          <t>1271356-186-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,22 +2395,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2331,14 +2423,18 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11677.4</v>
+        <v>51654.25</v>
       </c>
     </row>
     <row r="32">
@@ -2392,7 +2488,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2553,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2618,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2588,7 +2700,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1271356-186-CM25</t>
+          <t>2429-2700-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,22 +2720,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2636,14 +2748,18 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>51654.25</v>
+        <v>11677.4</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2813,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2878,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2943,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3195,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3076,7 +3212,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1293138-260-CM25</t>
+          <t>2452-3208-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3237,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3252,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>98730.73</v>
+        <v>53340.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2345-641-CM25</t>
+          <t>1413007-87-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,48 +3297,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.804.007-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>21446.36</v>
+        <v>6757.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057049-23302-CM25</t>
+          <t>5153-2309-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,17 +3362,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3382,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3397,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7334.69</v>
+        <v>151081.97</v>
       </c>
     </row>
     <row r="47">
@@ -3307,7 +3451,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3320,7 +3468,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079566-464-CM25</t>
+          <t>1057049-23302-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3493,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10.595.925-7</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8347.959999999999</v>
+        <v>7334.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5153-2309-CM25</t>
+          <t>2345-641-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,12 +3558,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,28 +3573,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>151081.97</v>
+        <v>21446.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1413007-87-CM25</t>
+          <t>1293138-260-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,27 +3623,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.804.007-2</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3653,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6757.25</v>
+        <v>98730.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2452-3208-CM25</t>
+          <t>1079566-464-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,27 +3684,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,18 +3714,18 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>53340.87</v>
+        <v>8347.959999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3453-566-CM25</t>
+          <t>2410-675-SE25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3579,7 +3735,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,43 +3745,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t xml:space="preserve">Rescatelife limitada </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.217.441-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>49428.69</v>
+        <v>5850.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3276-33-CM25</t>
+          <t>3453-566-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3800,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3810,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3840,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8774.059999999999</v>
+        <v>49428.69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1422309-36-CM25</t>
+          <t>3276-33-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,97 +3871,170 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7032.93</v>
+        <v>8774.059999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>1422309-36-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.979.490-7</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>7032.93</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>696750-48-CM25</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>oct-2025</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>61.935.400-1</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Los Ríos</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>MELMAN SPA</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="n">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
         <v>9042.18</v>
       </c>
     </row>
